--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251103_201831.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
